--- a/tiflow-erezept/develop/2.0.0-ballot.2/CodeSystem-tiflow-erezept-operation-outcome-details-cs.xlsx
+++ b/tiflow-erezept/develop/2.0.0-ballot.2/CodeSystem-tiflow-erezept-operation-outcome-details-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>8</t>
+    <t>11</t>
   </si>
   <si>
     <t>Level</t>
@@ -214,6 +214,33 @@
   </si>
   <si>
     <t>The multiple prescription part is not redeemable yet because its redemption period has not started</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_NO_PRESCRIPTIONS_FOUND</t>
+  </si>
+  <si>
+    <t>No prescriptions found</t>
+  </si>
+  <si>
+    <t>No redeemable prescriptions were found for the requested query scope</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_NOT_ACTIVATED</t>
+  </si>
+  <si>
+    <t>EU redemption not activated</t>
+  </si>
+  <si>
+    <t>The addressed task is not activated for EU redemption</t>
+  </si>
+  <si>
+    <t>TIFLOW_EREZEPT_COUNTRY_CODE_INVALID</t>
+  </si>
+  <si>
+    <t>Country code invalid</t>
+  </si>
+  <si>
+    <t>The provided country code is not supported for ePrescription or eDispensation processing</t>
   </si>
 </sst>
 </file>
@@ -525,7 +552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -654,6 +681,48 @@
         <v>66</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
